--- a/AAII_Financials/Yearly/FUJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUJIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>FUJIY</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21112300</v>
+      </c>
+      <c r="E8" s="3">
         <v>21341400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19575700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21507200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20799600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19824000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21515800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21942900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22912000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15651400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18083800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21261900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22350000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20131600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19845400</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12499300</v>
+      </c>
+      <c r="E9" s="3">
         <v>12659600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11732900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12947100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12291000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11960600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12645200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12940800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13778600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9378800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10964400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13060300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13913200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12400500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12001200</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8613000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8681800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7842800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8560100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8508500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7863500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8870600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9002000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9133400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6272500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7119400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8201700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8436700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7731000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7844200</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>992400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1091200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1038700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1159600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1239600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1375700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1467300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1409000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1566100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1080000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1198200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1374600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1505500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1528500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1567300</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,38 +998,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E14" s="3">
         <v>20700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-163100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-36700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-441000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>205200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-482300</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -1021,48 +1040,51 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>175400</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1084100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1092300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>991800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1069800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1095200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1116000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1139900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1172600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1201800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18909800</v>
+      </c>
+      <c r="E17" s="3">
         <v>19136600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17746100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19453000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18908000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18327900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19781900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20049300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21681500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14490200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16756200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19791400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21060200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19094300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18999800</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2202500</v>
+      </c>
+      <c r="E18" s="3">
         <v>2204700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1829500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2054200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1891600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1496200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1733900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1893600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1230400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1161200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1327600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1470600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1289800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1037300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>845700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-50700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-107500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-88800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-305400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-212600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-65600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-19200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-142000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>183900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>44000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>249700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>188000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>85700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3367300</v>
+      </c>
+      <c r="E21" s="3">
         <v>3347800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2928800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3212800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3292200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2824700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2939400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3085300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2574300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2141500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2281400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2780900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2779100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2412600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2174500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E22" s="3">
         <v>58400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>56100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>19100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>21500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>43000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>32300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>32200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>38300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30900</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2317900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2265600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2124900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2158100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2252900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2161600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1620900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1923800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1870700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1312800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1339500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1681300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1439500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1083400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>806300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E24" s="3">
         <v>518200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>516400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>490500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>470500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>502800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>335600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>505900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>512500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>297400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>356100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>498900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>501000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>406700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>271500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1747500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1608500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1667500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1782400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1658800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1285300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1418000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1358200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1015400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>983400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1182400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>938500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>676800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>534800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1738400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1741100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1608700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1649700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1738700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1638400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1161600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1246300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1324700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>886400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>855600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1011300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>741900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>493300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>395600</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E32" s="3">
         <v>50700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>107500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>88800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>305400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>212600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>65600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>19200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>142000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-183900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-44000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-249700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-188000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-85700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1740400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1742600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1609900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1650600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1739100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1638400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1161600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1246300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1324700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>886400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>855600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1011300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>741900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>493300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>395600</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1740400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1742600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1609900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1650600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1739100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1638400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1161600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1246300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1324700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>886400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>855600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1011300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>741900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>493300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>395600</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1072600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1149300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1188200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2020600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4004900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3569600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3681100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5908700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7233600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5904000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4416600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6200400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5537900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4048600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2125300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2148,365 +2237,389 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>40700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>205900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>162400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>152400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>111800</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4795500</v>
+      </c>
+      <c r="E43" s="3">
         <v>4674400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4605400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4762100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4929700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5476700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5189700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5575300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5828800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4285200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4730200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5809000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5833200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5352900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5030600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3778500</v>
+      </c>
+      <c r="E44" s="3">
         <v>3632600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3621700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4267500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4154200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3776400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3540000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3379300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3402100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2286500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2566400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3177500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3331900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3635400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3416700</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1164500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1105900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>995200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1219700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1114200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>806500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1429200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>757200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1056000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1198200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1062800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1226300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1281800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1122000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1266400</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10811200</v>
+      </c>
+      <c r="E46" s="3">
         <v>10562300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10410400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12270100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14203000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13629200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13839900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15620500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17520900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13714600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12981900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16575600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16137100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14192100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11950800</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3219400</v>
+      </c>
+      <c r="E47" s="3">
         <v>3005100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2644800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2237000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2681700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2682000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2151700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2426100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2540000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2018900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2349600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3249200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3045300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2927600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2558900</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15335800</v>
+      </c>
+      <c r="E48" s="3">
         <v>12687700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9889500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7961700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6754500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6450800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6280600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4754100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5061400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3508900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3914600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4498500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4857000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4964300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5007400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8447300</v>
+      </c>
+      <c r="E49" s="3">
         <v>8516800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8423900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8405000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8732800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9028800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8246500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7719500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7308300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3884100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4359400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4992000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4630300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4567600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3954500</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,9 +2716,12 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2630,27 +2749,30 @@
       <c r="K52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M52" s="3">
         <v>687200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>737400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1022100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>889300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1160100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1295000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>38072900</v>
+      </c>
+      <c r="E54" s="3">
         <v>35058300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31625100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31100500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32571400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32090700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30870200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30815700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32888700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23813700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24343000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30337500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29559000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27811700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24766600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1840800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1876700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1745800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1863300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2069600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1978000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1830200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1918600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2140900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1603800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1717900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2151700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2275700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2093300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2336000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2040600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1647300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2311900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1031500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1907100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>837900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1363300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1539400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>392400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>835800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>406500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>312600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>409700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>369800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1614000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2271000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2306800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1989300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2036300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2222100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1874700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1341900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1229800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1651900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2144900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2335700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2843800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2777800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2503400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2309100</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7913400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7518900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7707800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6697500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8066700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6476400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6133800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6337700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6254100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4584400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4460000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5308100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5463200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4966400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6259000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4418400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3710200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1705300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2448300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2503100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4469300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5165500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3190400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3884000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2930800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2281400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2670300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2885100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2886900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>183800</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>595000</v>
+      </c>
+      <c r="E62" s="3">
         <v>593500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>493000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>448400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>533900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>489500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>527200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>485000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>518100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1011700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1196400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1312100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1075000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1553100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1541100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13895100</v>
+      </c>
+      <c r="E66" s="3">
         <v>12669500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10645200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10128700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11778700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11998700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12341200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10557300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11244600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10040100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9534000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11292500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11050000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10823700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9201800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19605700</v>
+      </c>
+      <c r="E72" s="3">
         <v>19567200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18124500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19680400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23616500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24437500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23820100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22630800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22445200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15337700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15986000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18135400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18653900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17994100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17578800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24147400</v>
+      </c>
+      <c r="E76" s="3">
         <v>22360800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20953000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20785800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20609200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19933000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18152600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18382500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19576600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13773600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14809000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19045100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18509100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16988000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15564800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1740400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1742600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1609900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1650600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1739100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1638400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1161600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1246300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1324700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>886400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>855600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1011300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>741900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>493300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>395600</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1084100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1092300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>991800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1069800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1095200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1116000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1139900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1172600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1201800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>792900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>918500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1048400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1295600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1286700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1335900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2582000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2859200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2697000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1583100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2667600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3805300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2376000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2250200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2458900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1945300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1642600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2249600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2679600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1813000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1221600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3280300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3357600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2763300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2029900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1038000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-904700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-786900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-618600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-593600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-503100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-469000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-485700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-643800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-816900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-910900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3488000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3619100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3486900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2431500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1264400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2526100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2275500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1882400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1052500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-784800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1156300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1027900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1149400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1281100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1680300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>530500</v>
+      </c>
+      <c r="E96" s="3">
         <v>455800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>371400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>346900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>354400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>343400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>332900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>299300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-203300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-235000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-226100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-176600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-164200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-141500</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>756300</v>
+      </c>
+      <c r="E100" s="3">
         <v>727100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-930500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-866200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1474600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2332100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1385500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2438300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>750100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1261700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-388900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-229900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1166100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-220600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>205200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>141000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>216800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>183700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-172200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>17700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-56700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-150600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>210600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>157700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>213500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-25500</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-50800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-587700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1637800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>753800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2403800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1024300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1014200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1853900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-926000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1043400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1458100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1911500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-704800</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
